--- a/demo/pq-web.xlsx
+++ b/demo/pq-web.xlsx
@@ -125,5 +125,5 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<DataMashup xmlns="http://schemas.microsoft.com/DataMashup">AAAAAEgDAABQSwMEFAAAAAgAa7r1XH+/08qcAAAA5AAAABMAAABbQ29udGVudF9UeXBlc10ueG1sbY5LDsIwDESvEnmfurBACDXtArgBF4iC+xHNR42Lwu1J6A516Zl5nmm6ZGfxpiVO3ik4VDUIcsY/JzcoWLmXZ+ja5vEJFEWOuqhgZA4XxGhGsjpWPpDLTu8Xqzmfy4BBm5ceCI91fULjHZNjyeUHtM2Ner3OLO4py1ttxkFct1ypUsCUGIuMu4D9i+sQ5sloziYmaaO0BcTf7PYLUEsDBBQAAAAIAGu69Vy5xFaLhwAAALsAAAASAAAAQ29uZmlnL1BhY2thZ2UueG1sTY3BCgIhFEV/RdyPb2oV8XQWtR0IovZiziiNOugz+vwGSmh3D9x7Dw7vsLCXzcWnKPlO9JzZaNLDx1nySlN34IPCizZPPVu2lWOR3BGtR4BinA26iOBNTiVNJEwKcNakR11cXeE34wrvX4Paix6hAY4+tryZEf4YT3Whmq2ysbtdERpiO1UfUEsDBBQAAAAIAGu69VzSDPzruwAAABsBAAATAAAARm9ybXVsYXMvU2VjdGlvbjEubV2NPwvCMBDF93yKkCmFWnEWpzq4qbTgnNYTC0lOchdFpN/dtLVQvOX+vHvvR9Byh15WU99shaC7CXCVx8iPyHInLbCQqSqMoYV0qE1joTgFdMhwAHOFQLqkZ7HHNjrwrC/QFCV6TjNptX5BsyJjgYqWnirLsnwMrN+PxJnz6mA83TC4Em10fhBJT8xcfj7qHI3njt8ql5w06aNrIPRJUzWysX/3/gepMPCCMqx6BI+hs3OT/kXnF46t+AJQSwECFAAUAAAACABruvVcf7/TypwAAADkAAAAEwAAAAAAAAAAAAAAAAAAAAAAW0NvbnRlbnRfVHlwZXNdLnhtbFBLAQIUABQAAAAIAGu69Vy5xFaLhwAAALsAAAASAAAAAAAAAAAAAAAAAM0AAABDb25maWcvUGFja2FnZS54bWxQSwECFAAUAAAACABruvVc0gz867sAAAAbAQAAEwAAAAAAAAAAAAAAAACEAQAARm9ybXVsYXMvU2VjdGlvbjEubVBLBQYAAAAAAwADAMIAAABwAgAAAADXAAAAPD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXRmLTgiPz48UGVybWlzc2lvbkxpc3QgeG1sbnM6eHNkPSJodHRwOi8vd3d3LnczLm9yZy8yMDAxL1hNTFNjaGVtYSI+PENhbkV2YWx1YXRlRnV0dXJlUGFja2FnZXM+ZmFsc2U8L0NhbkV2YWx1YXRlRnV0dXJlUGFja2FnZXM+PEZpcmV3YWxsRW5hYmxlZD50cnVlPC9GaXJld2FsbEVuYWJsZWQ+PC9QZXJtaXNzaW9uTGlzdD4AAAAAAAAAAA==</DataMashup>
+<DataMashup xmlns="http://schemas.microsoft.com/DataMashup">AAAAAEgDAABQSwMEFAAAAAgAwr71XH+/08qcAAAA5AAAABMAAABbQ29udGVudF9UeXBlc10ueG1sbY5LDsIwDESvEnmfurBACDXtArgBF4iC+xHNR42Lwu1J6A516Zl5nmm6ZGfxpiVO3ik4VDUIcsY/JzcoWLmXZ+ja5vEJFEWOuqhgZA4XxGhGsjpWPpDLTu8Xqzmfy4BBm5ceCI91fULjHZNjyeUHtM2Ner3OLO4py1ttxkFct1ypUsCUGIuMu4D9i+sQ5sloziYmaaO0BcTf7PYLUEsDBBQAAAAIAMK+9Vy5xFaLhwAAALsAAAASAAAAQ29uZmlnL1BhY2thZ2UueG1sTY3BCgIhFEV/RdyPb2oV8XQWtR0IovZiziiNOugz+vwGSmh3D9x7Dw7vsLCXzcWnKPlO9JzZaNLDx1nySlN34IPCizZPPVu2lWOR3BGtR4BinA26iOBNTiVNJEwKcNakR11cXeE34wrvX4Paix6hAY4+tryZEf4YT3Whmq2ysbtdERpiO1UfUEsDBBQAAAAIAMK+9VzSDPzruwAAABsBAAATAAAARm9ybXVsYXMvU2VjdGlvbjEubV2NPwvCMBDF93yKkCmFWnEWpzq4qbTgnNYTC0lOchdFpN/dtLVQvOX+vHvvR9Byh15WU99shaC7CXCVx8iPyHInLbCQqSqMoYV0qE1joTgFdMhwAHOFQLqkZ7HHNjrwrC/QFCV6TjNptX5BsyJjgYqWnirLsnwMrN+PxJnz6mA83TC4Em10fhBJT8xcfj7qHI3njt8ql5w06aNrIPRJUzWysX/3/gepMPCCMqx6BI+hs3OT/kXnF46t+AJQSwECFAAUAAAACADCvvVcf7/TypwAAADkAAAAEwAAAAAAAAAAAAAAAAAAAAAAW0NvbnRlbnRfVHlwZXNdLnhtbFBLAQIUABQAAAAIAMK+9Vy5xFaLhwAAALsAAAASAAAAAAAAAAAAAAAAAM0AAABDb25maWcvUGFja2FnZS54bWxQSwECFAAUAAAACADCvvVc0gz867sAAAAbAQAAEwAAAAAAAAAAAAAAAACEAQAARm9ybXVsYXMvU2VjdGlvbjEubVBLBQYAAAAAAwADAMIAAABwAgAAAADXAAAAPD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXRmLTgiPz48UGVybWlzc2lvbkxpc3QgeG1sbnM6eHNkPSJodHRwOi8vd3d3LnczLm9yZy8yMDAxL1hNTFNjaGVtYSI+PENhbkV2YWx1YXRlRnV0dXJlUGFja2FnZXM+ZmFsc2U8L0NhbkV2YWx1YXRlRnV0dXJlUGFja2FnZXM+PEZpcmV3YWxsRW5hYmxlZD50cnVlPC9GaXJld2FsbEVuYWJsZWQ+PC9QZXJtaXNzaW9uTGlzdD4AAAAAAAAAAA==</DataMashup>
 </file>
--- a/demo/pq-web.xlsx
+++ b/demo/pq-web.xlsx
@@ -125,5 +125,5 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<DataMashup xmlns="http://schemas.microsoft.com/DataMashup">AAAAAEgDAABQSwMEFAAAAAgAwr71XH+/08qcAAAA5AAAABMAAABbQ29udGVudF9UeXBlc10ueG1sbY5LDsIwDESvEnmfurBACDXtArgBF4iC+xHNR42Lwu1J6A516Zl5nmm6ZGfxpiVO3ik4VDUIcsY/JzcoWLmXZ+ja5vEJFEWOuqhgZA4XxGhGsjpWPpDLTu8Xqzmfy4BBm5ceCI91fULjHZNjyeUHtM2Ner3OLO4py1ttxkFct1ypUsCUGIuMu4D9i+sQ5sloziYmaaO0BcTf7PYLUEsDBBQAAAAIAMK+9Vy5xFaLhwAAALsAAAASAAAAQ29uZmlnL1BhY2thZ2UueG1sTY3BCgIhFEV/RdyPb2oV8XQWtR0IovZiziiNOugz+vwGSmh3D9x7Dw7vsLCXzcWnKPlO9JzZaNLDx1nySlN34IPCizZPPVu2lWOR3BGtR4BinA26iOBNTiVNJEwKcNakR11cXeE34wrvX4Paix6hAY4+tryZEf4YT3Whmq2ysbtdERpiO1UfUEsDBBQAAAAIAMK+9VzSDPzruwAAABsBAAATAAAARm9ybXVsYXMvU2VjdGlvbjEubV2NPwvCMBDF93yKkCmFWnEWpzq4qbTgnNYTC0lOchdFpN/dtLVQvOX+vHvvR9Byh15WU99shaC7CXCVx8iPyHInLbCQqSqMoYV0qE1joTgFdMhwAHOFQLqkZ7HHNjrwrC/QFCV6TjNptX5BsyJjgYqWnirLsnwMrN+PxJnz6mA83TC4Em10fhBJT8xcfj7qHI3njt8ql5w06aNrIPRJUzWysX/3/gepMPCCMqx6BI+hs3OT/kXnF46t+AJQSwECFAAUAAAACADCvvVcf7/TypwAAADkAAAAEwAAAAAAAAAAAAAAAAAAAAAAW0NvbnRlbnRfVHlwZXNdLnhtbFBLAQIUABQAAAAIAMK+9Vy5xFaLhwAAALsAAAASAAAAAAAAAAAAAAAAAM0AAABDb25maWcvUGFja2FnZS54bWxQSwECFAAUAAAACADCvvVc0gz867sAAAAbAQAAEwAAAAAAAAAAAAAAAACEAQAARm9ybXVsYXMvU2VjdGlvbjEubVBLBQYAAAAAAwADAMIAAABwAgAAAADXAAAAPD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXRmLTgiPz48UGVybWlzc2lvbkxpc3QgeG1sbnM6eHNkPSJodHRwOi8vd3d3LnczLm9yZy8yMDAxL1hNTFNjaGVtYSI+PENhbkV2YWx1YXRlRnV0dXJlUGFja2FnZXM+ZmFsc2U8L0NhbkV2YWx1YXRlRnV0dXJlUGFja2FnZXM+PEZpcmV3YWxsRW5hYmxlZD50cnVlPC9GaXJld2FsbEVuYWJsZWQ+PC9QZXJtaXNzaW9uTGlzdD4AAAAAAAAAAA==</DataMashup>
+<DataMashup xmlns="http://schemas.microsoft.com/DataMashup">AAAAAEgDAABQSwMEFAAAAAgAeUD2XH+/08qcAAAA5AAAABMAAABbQ29udGVudF9UeXBlc10ueG1sbY5LDsIwDESvEnmfurBACDXtArgBF4iC+xHNR42Lwu1J6A516Zl5nmm6ZGfxpiVO3ik4VDUIcsY/JzcoWLmXZ+ja5vEJFEWOuqhgZA4XxGhGsjpWPpDLTu8Xqzmfy4BBm5ceCI91fULjHZNjyeUHtM2Ner3OLO4py1ttxkFct1ypUsCUGIuMu4D9i+sQ5sloziYmaaO0BcTf7PYLUEsDBBQAAAAIAHlA9ly5xFaLhwAAALsAAAASAAAAQ29uZmlnL1BhY2thZ2UueG1sTY3BCgIhFEV/RdyPb2oV8XQWtR0IovZiziiNOugz+vwGSmh3D9x7Dw7vsLCXzcWnKPlO9JzZaNLDx1nySlN34IPCizZPPVu2lWOR3BGtR4BinA26iOBNTiVNJEwKcNakR11cXeE34wrvX4Paix6hAY4+tryZEf4YT3Whmq2ysbtdERpiO1UfUEsDBBQAAAAIAHlA9lzSDPzruwAAABsBAAATAAAARm9ybXVsYXMvU2VjdGlvbjEubV2NPwvCMBDF93yKkCmFWnEWpzq4qbTgnNYTC0lOchdFpN/dtLVQvOX+vHvvR9Byh15WU99shaC7CXCVx8iPyHInLbCQqSqMoYV0qE1joTgFdMhwAHOFQLqkZ7HHNjrwrC/QFCV6TjNptX5BsyJjgYqWnirLsnwMrN+PxJnz6mA83TC4Em10fhBJT8xcfj7qHI3njt8ql5w06aNrIPRJUzWysX/3/gepMPCCMqx6BI+hs3OT/kXnF46t+AJQSwECFAAUAAAACAB5QPZcf7/TypwAAADkAAAAEwAAAAAAAAAAAAAAAAAAAAAAW0NvbnRlbnRfVHlwZXNdLnhtbFBLAQIUABQAAAAIAHlA9ly5xFaLhwAAALsAAAASAAAAAAAAAAAAAAAAAM0AAABDb25maWcvUGFja2FnZS54bWxQSwECFAAUAAAACAB5QPZc0gz867sAAAAbAQAAEwAAAAAAAAAAAAAAAACEAQAARm9ybXVsYXMvU2VjdGlvbjEubVBLBQYAAAAAAwADAMIAAABwAgAAAADXAAAAPD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXRmLTgiPz48UGVybWlzc2lvbkxpc3QgeG1sbnM6eHNkPSJodHRwOi8vd3d3LnczLm9yZy8yMDAxL1hNTFNjaGVtYSI+PENhbkV2YWx1YXRlRnV0dXJlUGFja2FnZXM+ZmFsc2U8L0NhbkV2YWx1YXRlRnV0dXJlUGFja2FnZXM+PEZpcmV3YWxsRW5hYmxlZD50cnVlPC9GaXJld2FsbEVuYWJsZWQ+PC9QZXJtaXNzaW9uTGlzdD4AAAAAAAAAAA==</DataMashup>
 </file>